--- a/backtest_runs/20260410_193731/by_symbol/PRET/PRET.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PRET/PRET.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-452.8699999999908</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>99547.13</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>99547.13</v>
@@ -863,7 +863,7 @@
         <v>-10646.24</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>88900.89000000001</v>
@@ -909,7 +909,7 @@
         <v>-20.23999999999597</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>88880.65000000002</v>
@@ -1001,7 +1001,7 @@
         <v>-5113.130000000009</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>83767.52</v>
